--- a/database/excels/organization/base-seeder.xlsx
+++ b/database/excels/organization/base-seeder.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/monoland/Platform/monoland/database/excels/organization/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFD053AE-C7E5-5A4E-8ED3-4DFCA4450E81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B79BF79C-9FC1-9C4B-BFF6-A425A59C9FDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" activeTab="1" xr2:uid="{94E1010F-4E68-D749-BBCF-3803F804C4FE}"/>
+    <workbookView xWindow="20" yWindow="500" windowWidth="33580" windowHeight="20500" activeTab="2" xr2:uid="{94E1010F-4E68-D749-BBCF-3803F804C4FE}"/>
   </bookViews>
   <sheets>
     <sheet name="module" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="119">
   <si>
     <t>name</t>
   </si>
@@ -146,15 +146,6 @@
     <t>Analisa Kekosongan Jabatan</t>
   </si>
   <si>
-    <t>Pelaksana</t>
-  </si>
-  <si>
-    <t>Fungsional</t>
-  </si>
-  <si>
-    <t>Struktural</t>
-  </si>
-  <si>
     <t>Jabatan Pelaksana</t>
   </si>
   <si>
@@ -164,9 +155,6 @@
     <t>Jabatan Struktural</t>
   </si>
   <si>
-    <t>Unit Organisasi</t>
-  </si>
-  <si>
     <t>organization-dashboard</t>
   </si>
   <si>
@@ -194,15 +182,6 @@
     <t>organization-report</t>
   </si>
   <si>
-    <t>hiking</t>
-  </si>
-  <si>
-    <t>engineering</t>
-  </si>
-  <si>
-    <t>account_circle</t>
-  </si>
-  <si>
     <t>format_color_fill</t>
   </si>
   <si>
@@ -215,15 +194,9 @@
     <t>executor</t>
   </si>
   <si>
-    <t>functional</t>
-  </si>
-  <si>
     <t>structural</t>
   </si>
   <si>
-    <t>workunit</t>
-  </si>
-  <si>
     <t>emptiness</t>
   </si>
   <si>
@@ -237,6 +210,183 @@
   </si>
   <si>
     <t>superadmin, administrator</t>
+  </si>
+  <si>
+    <t>Peta Jabatan</t>
+  </si>
+  <si>
+    <t>Jenis Jabatan</t>
+  </si>
+  <si>
+    <t>Jenis Peta Jabatan</t>
+  </si>
+  <si>
+    <t>Peta Fungsional</t>
+  </si>
+  <si>
+    <t>Spesifikasi Fungsional</t>
+  </si>
+  <si>
+    <t>Tingkat Fungsional</t>
+  </si>
+  <si>
+    <t>Peta Eselon</t>
+  </si>
+  <si>
+    <t>Eselon</t>
+  </si>
+  <si>
+    <t>Unit Kerja</t>
+  </si>
+  <si>
+    <t>S.O.T.K</t>
+  </si>
+  <si>
+    <t>Analisa Jabatan</t>
+  </si>
+  <si>
+    <t>Rumpun Fungsional</t>
+  </si>
+  <si>
+    <t>organization-positionmap</t>
+  </si>
+  <si>
+    <t>organization-positiontype</t>
+  </si>
+  <si>
+    <t>organization-positionkind</t>
+  </si>
+  <si>
+    <t>organization-functionalstage</t>
+  </si>
+  <si>
+    <t>organization-functionalgrade</t>
+  </si>
+  <si>
+    <t>organization-functionalmap</t>
+  </si>
+  <si>
+    <t>organization-functionalexpert</t>
+  </si>
+  <si>
+    <t>organization-echelonmap</t>
+  </si>
+  <si>
+    <t>organization-echhelon</t>
+  </si>
+  <si>
+    <t>Peta Unit Kerja</t>
+  </si>
+  <si>
+    <t>organization-workunitype</t>
+  </si>
+  <si>
+    <t>organization-composition</t>
+  </si>
+  <si>
+    <t>organization-formation</t>
+  </si>
+  <si>
+    <t>positionmap</t>
+  </si>
+  <si>
+    <t>positionkind</t>
+  </si>
+  <si>
+    <t>functionalstage</t>
+  </si>
+  <si>
+    <t>functionalmap</t>
+  </si>
+  <si>
+    <t>echelonmap</t>
+  </si>
+  <si>
+    <t>workunitype</t>
+  </si>
+  <si>
+    <t>positionmap/:positionmap/positiontype</t>
+  </si>
+  <si>
+    <t>functionalstage/:functionalstage/functionalgrade</t>
+  </si>
+  <si>
+    <t>functionalmap/:functionalmap/functionalexpert</t>
+  </si>
+  <si>
+    <t>functionalmap/:functionalmap/functional</t>
+  </si>
+  <si>
+    <t>organization-functionalread</t>
+  </si>
+  <si>
+    <t>echelonmap/:echelonmap/echhelon</t>
+  </si>
+  <si>
+    <t>workunitype/:workunitype/workunit</t>
+  </si>
+  <si>
+    <t>organization-workunitread</t>
+  </si>
+  <si>
+    <t>view, show</t>
+  </si>
+  <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t>picture_in_picture</t>
+  </si>
+  <si>
+    <t>highlight</t>
+  </si>
+  <si>
+    <t>layers</t>
+  </si>
+  <si>
+    <t>radio</t>
+  </si>
+  <si>
+    <t>psychology</t>
+  </si>
+  <si>
+    <t>folder_special</t>
+  </si>
+  <si>
+    <t>confirmation_number</t>
+  </si>
+  <si>
+    <t>paragliding</t>
+  </si>
+  <si>
+    <t>swap_horizontal_circle</t>
+  </si>
+  <si>
+    <t>event_seat</t>
+  </si>
+  <si>
+    <t>room_preferences</t>
+  </si>
+  <si>
+    <t>maps_home_work</t>
+  </si>
+  <si>
+    <t>developer_board</t>
+  </si>
+  <si>
+    <t>fact_check</t>
+  </si>
+  <si>
+    <t>functionalread</t>
+  </si>
+  <si>
+    <t>workunitread</t>
+  </si>
+  <si>
+    <t>workunitread/:workunitread/composition</t>
+  </si>
+  <si>
+    <t>workunitread/:workunitread/formation</t>
   </si>
 </sst>
 </file>
@@ -674,17 +824,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CF7F25A-0145-E049-BABB-6C723A859E1D}">
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="27.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27.5" customWidth="1"/>
-    <col min="4" max="4" width="23.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.1640625" customWidth="1"/>
     <col min="5" max="5" width="17" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="51.83203125" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="10.83203125" style="4"/>
-    <col min="10" max="10" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="25.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
@@ -727,7 +877,7 @@
         <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E2" t="s">
         <v>11</v>
@@ -750,22 +900,22 @@
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="C3" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="D3" t="s">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="E3" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="F3" t="s">
         <v>28</v>
       </c>
       <c r="G3" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="H3" s="4" t="b">
         <v>0</v>
@@ -779,28 +929,31 @@
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="C4" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="D4" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="E4" t="s">
-        <v>55</v>
+        <v>101</v>
       </c>
       <c r="F4" t="s">
         <v>28</v>
       </c>
       <c r="G4" t="s">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="H4" s="4" t="b">
         <v>0</v>
       </c>
       <c r="I4" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="J4" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -808,22 +961,22 @@
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="D5" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="E5" t="s">
-        <v>56</v>
+        <v>102</v>
       </c>
       <c r="F5" t="s">
         <v>28</v>
       </c>
       <c r="G5" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="H5" s="4" t="b">
         <v>0</v>
@@ -837,22 +990,22 @@
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="C6" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="D6" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="E6" t="s">
-        <v>29</v>
+        <v>103</v>
       </c>
       <c r="F6" t="s">
         <v>28</v>
       </c>
       <c r="G6" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="H6" s="4" t="b">
         <v>0</v>
@@ -866,28 +1019,31 @@
         <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="D7" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="E7" t="s">
-        <v>57</v>
+        <v>104</v>
       </c>
       <c r="F7" t="s">
         <v>28</v>
       </c>
       <c r="G7" t="s">
-        <v>64</v>
+        <v>92</v>
       </c>
       <c r="H7" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" s="4" t="b">
         <v>0</v>
+      </c>
+      <c r="J7" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
@@ -895,28 +1051,28 @@
         <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="D8" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="E8" t="s">
-        <v>58</v>
+        <v>105</v>
       </c>
       <c r="F8" t="s">
         <v>28</v>
       </c>
       <c r="G8" t="s">
-        <v>65</v>
+        <v>88</v>
       </c>
       <c r="H8" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8" s="4" t="b">
         <v>1</v>
-      </c>
-      <c r="I8" s="4" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
@@ -924,28 +1080,31 @@
         <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="D9" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="E9" t="s">
-        <v>59</v>
+        <v>106</v>
       </c>
       <c r="F9" t="s">
         <v>28</v>
       </c>
       <c r="G9" t="s">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="H9" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" s="4" t="b">
         <v>0</v>
+      </c>
+      <c r="J9" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
@@ -953,27 +1112,448 @@
         <v>28</v>
       </c>
       <c r="B10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" t="s">
+        <v>107</v>
+      </c>
+      <c r="F10" t="s">
+        <v>28</v>
+      </c>
+      <c r="G10" t="s">
+        <v>94</v>
+      </c>
+      <c r="H10" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I10" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" t="s">
+        <v>95</v>
+      </c>
+      <c r="E11" t="s">
+        <v>107</v>
+      </c>
+      <c r="F11" t="s">
+        <v>28</v>
+      </c>
+      <c r="G11" t="s">
+        <v>115</v>
+      </c>
+      <c r="H11" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I11" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" t="s">
+        <v>42</v>
+      </c>
+      <c r="E12" t="s">
+        <v>108</v>
+      </c>
+      <c r="F12" t="s">
+        <v>28</v>
+      </c>
+      <c r="G12" t="s">
+        <v>53</v>
+      </c>
+      <c r="H12" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I12" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D13" t="s">
+        <v>79</v>
+      </c>
+      <c r="E13" t="s">
+        <v>109</v>
+      </c>
+      <c r="F13" t="s">
+        <v>28</v>
+      </c>
+      <c r="G13" t="s">
+        <v>89</v>
+      </c>
+      <c r="H13" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I13" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" t="s">
+        <v>67</v>
+      </c>
+      <c r="C14" t="s">
+        <v>67</v>
+      </c>
+      <c r="D14" t="s">
+        <v>80</v>
+      </c>
+      <c r="E14" t="s">
+        <v>110</v>
+      </c>
+      <c r="F14" t="s">
+        <v>28</v>
+      </c>
+      <c r="G14" t="s">
+        <v>96</v>
+      </c>
+      <c r="H14" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I14" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15" t="s">
+        <v>44</v>
+      </c>
+      <c r="E15" t="s">
+        <v>29</v>
+      </c>
+      <c r="F15" t="s">
+        <v>28</v>
+      </c>
+      <c r="G15" t="s">
+        <v>54</v>
+      </c>
+      <c r="H15" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I15" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" t="s">
+        <v>81</v>
+      </c>
+      <c r="C16" t="s">
+        <v>81</v>
+      </c>
+      <c r="D16" t="s">
+        <v>82</v>
+      </c>
+      <c r="E16" t="s">
+        <v>111</v>
+      </c>
+      <c r="F16" t="s">
+        <v>28</v>
+      </c>
+      <c r="G16" t="s">
+        <v>90</v>
+      </c>
+      <c r="H16" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I16" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17" t="s">
+        <v>68</v>
+      </c>
+      <c r="C17" t="s">
+        <v>68</v>
+      </c>
+      <c r="D17" t="s">
+        <v>45</v>
+      </c>
+      <c r="E17" t="s">
+        <v>112</v>
+      </c>
+      <c r="F17" t="s">
+        <v>28</v>
+      </c>
+      <c r="G17" t="s">
+        <v>97</v>
+      </c>
+      <c r="H17" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I17" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J17" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" t="s">
+        <v>68</v>
+      </c>
+      <c r="C18" t="s">
+        <v>68</v>
+      </c>
+      <c r="D18" t="s">
+        <v>98</v>
+      </c>
+      <c r="E18" t="s">
+        <v>112</v>
+      </c>
+      <c r="F18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G18" t="s">
+        <v>116</v>
+      </c>
+      <c r="H18" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I18" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" t="s">
+        <v>69</v>
+      </c>
+      <c r="C19" t="s">
+        <v>69</v>
+      </c>
+      <c r="D19" t="s">
+        <v>83</v>
+      </c>
+      <c r="E19" t="s">
+        <v>113</v>
+      </c>
+      <c r="F19" t="s">
+        <v>28</v>
+      </c>
+      <c r="G19" t="s">
+        <v>117</v>
+      </c>
+      <c r="H19" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I19" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" t="s">
+        <v>70</v>
+      </c>
+      <c r="C20" t="s">
+        <v>70</v>
+      </c>
+      <c r="D20" t="s">
+        <v>84</v>
+      </c>
+      <c r="E20" t="s">
+        <v>114</v>
+      </c>
+      <c r="F20" t="s">
+        <v>28</v>
+      </c>
+      <c r="G20" t="s">
+        <v>118</v>
+      </c>
+      <c r="H20" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I20" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J20" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" t="s">
+        <v>34</v>
+      </c>
+      <c r="C21" t="s">
+        <v>37</v>
+      </c>
+      <c r="D21" t="s">
+        <v>46</v>
+      </c>
+      <c r="E21" t="s">
+        <v>50</v>
+      </c>
+      <c r="F21" t="s">
+        <v>28</v>
+      </c>
+      <c r="G21" t="s">
+        <v>55</v>
+      </c>
+      <c r="H21" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I21" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22" t="s">
+        <v>36</v>
+      </c>
+      <c r="D22" t="s">
+        <v>47</v>
+      </c>
+      <c r="E22" t="s">
+        <v>51</v>
+      </c>
+      <c r="F22" t="s">
+        <v>28</v>
+      </c>
+      <c r="G22" t="s">
+        <v>56</v>
+      </c>
+      <c r="H22" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I22" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23" t="s">
+        <v>33</v>
+      </c>
+      <c r="C23" t="s">
+        <v>35</v>
+      </c>
+      <c r="D23" t="s">
+        <v>48</v>
+      </c>
+      <c r="E23" t="s">
+        <v>52</v>
+      </c>
+      <c r="F23" t="s">
+        <v>28</v>
+      </c>
+      <c r="G23" t="s">
+        <v>57</v>
+      </c>
+      <c r="H23" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I23" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>28</v>
+      </c>
+      <c r="B24" t="s">
         <v>23</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C24" t="s">
         <v>24</v>
       </c>
-      <c r="D10" t="s">
-        <v>53</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="D24" t="s">
+        <v>49</v>
+      </c>
+      <c r="E24" t="s">
         <v>26</v>
       </c>
-      <c r="F10" t="s">
-        <v>28</v>
-      </c>
-      <c r="G10" t="s">
+      <c r="F24" t="s">
+        <v>28</v>
+      </c>
+      <c r="G24" t="s">
         <v>25</v>
       </c>
-      <c r="H10" s="4" t="b">
+      <c r="H24" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="I10" s="4" t="b">
+      <c r="I24" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -984,10 +1564,11 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{462F859E-7489-7142-8B02-E1AE063A22DB}">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1007,7 +1588,7 @@
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>15</v>
@@ -1018,7 +1599,7 @@
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="C3" t="s">
         <v>21</v>
@@ -1029,7 +1610,7 @@
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="C4" t="s">
         <v>21</v>
@@ -1040,7 +1621,7 @@
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="C5" t="s">
         <v>21</v>
@@ -1051,7 +1632,7 @@
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="C6" t="s">
         <v>21</v>
@@ -1062,7 +1643,7 @@
         <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="C7" t="s">
         <v>21</v>
@@ -1073,7 +1654,7 @@
         <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="C8" t="s">
         <v>21</v>
@@ -1084,7 +1665,7 @@
         <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="C9" t="s">
         <v>21</v>
@@ -1095,9 +1676,163 @@
         <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="C10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" t="s">
+        <v>95</v>
+      </c>
+      <c r="C11" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" t="s">
+        <v>79</v>
+      </c>
+      <c r="C13" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" t="s">
+        <v>80</v>
+      </c>
+      <c r="C14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" t="s">
+        <v>82</v>
+      </c>
+      <c r="C16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" t="s">
+        <v>98</v>
+      </c>
+      <c r="C18" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" t="s">
+        <v>83</v>
+      </c>
+      <c r="C19" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" t="s">
+        <v>84</v>
+      </c>
+      <c r="C20" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" t="s">
+        <v>46</v>
+      </c>
+      <c r="C21" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" t="s">
+        <v>47</v>
+      </c>
+      <c r="C22" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23" t="s">
+        <v>48</v>
+      </c>
+      <c r="C23" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>28</v>
+      </c>
+      <c r="B24" t="s">
+        <v>49</v>
+      </c>
+      <c r="C24" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1136,7 +1871,7 @@
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -1146,9 +1881,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{279D8F2B-ACF8-DF40-AE6A-EC20C786574F}">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="1" max="1" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="33.33203125" customWidth="1"/>
     <col min="3" max="3" width="22.33203125" bestFit="1" customWidth="1"/>
   </cols>
@@ -1169,10 +1905,10 @@
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -1180,10 +1916,10 @@
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C3" t="s">
-        <v>46</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -1191,10 +1927,10 @@
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C4" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -1202,10 +1938,10 @@
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C5" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -1213,10 +1949,10 @@
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C6" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -1224,10 +1960,10 @@
         <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C7" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -1235,10 +1971,10 @@
         <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C8" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -1246,10 +1982,10 @@
         <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C9" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -1257,10 +1993,164 @@
         <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C10" t="s">
-        <v>53</v>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" t="s">
+        <v>59</v>
+      </c>
+      <c r="C12" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" t="s">
+        <v>59</v>
+      </c>
+      <c r="C13" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" t="s">
+        <v>59</v>
+      </c>
+      <c r="C14" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" t="s">
+        <v>59</v>
+      </c>
+      <c r="C15" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" t="s">
+        <v>59</v>
+      </c>
+      <c r="C16" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17" t="s">
+        <v>59</v>
+      </c>
+      <c r="C17" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" t="s">
+        <v>59</v>
+      </c>
+      <c r="C18" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" t="s">
+        <v>59</v>
+      </c>
+      <c r="C19" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" t="s">
+        <v>59</v>
+      </c>
+      <c r="C20" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" t="s">
+        <v>59</v>
+      </c>
+      <c r="C21" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C22" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23" t="s">
+        <v>59</v>
+      </c>
+      <c r="C23" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>28</v>
+      </c>
+      <c r="B24" t="s">
+        <v>59</v>
+      </c>
+      <c r="C24" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1270,12 +2160,12 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2E44C3F-3A12-F647-BCB1-FF7A86E9DA05}">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.33203125" customWidth="1"/>
     <col min="2" max="2" width="33.33203125" customWidth="1"/>
-    <col min="3" max="3" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
@@ -1297,10 +2187,10 @@
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D2" t="s">
         <v>17</v>
@@ -1311,10 +2201,10 @@
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C3" t="s">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="D3" t="s">
         <v>17</v>
@@ -1325,10 +2215,10 @@
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C4" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="D4" t="s">
         <v>17</v>
@@ -1339,10 +2229,10 @@
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C5" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="D5" t="s">
         <v>17</v>
@@ -1353,10 +2243,10 @@
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C6" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="D6" t="s">
         <v>17</v>
@@ -1367,10 +2257,10 @@
         <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C7" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D7" t="s">
         <v>17</v>
@@ -1381,10 +2271,10 @@
         <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C8" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="D8" t="s">
         <v>17</v>
@@ -1395,10 +2285,10 @@
         <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C9" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="D9" t="s">
         <v>17</v>
@@ -1409,12 +2299,208 @@
         <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C10" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="D10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11" t="s">
+        <v>95</v>
+      </c>
+      <c r="D11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" t="s">
+        <v>59</v>
+      </c>
+      <c r="C12" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" t="s">
+        <v>59</v>
+      </c>
+      <c r="C13" t="s">
+        <v>79</v>
+      </c>
+      <c r="D13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" t="s">
+        <v>59</v>
+      </c>
+      <c r="C14" t="s">
+        <v>80</v>
+      </c>
+      <c r="D14" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" t="s">
+        <v>59</v>
+      </c>
+      <c r="C15" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" t="s">
+        <v>59</v>
+      </c>
+      <c r="C16" t="s">
+        <v>82</v>
+      </c>
+      <c r="D16" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17" t="s">
+        <v>59</v>
+      </c>
+      <c r="C17" t="s">
+        <v>45</v>
+      </c>
+      <c r="D17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" t="s">
+        <v>59</v>
+      </c>
+      <c r="C18" t="s">
+        <v>98</v>
+      </c>
+      <c r="D18" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" t="s">
+        <v>59</v>
+      </c>
+      <c r="C19" t="s">
+        <v>83</v>
+      </c>
+      <c r="D19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" t="s">
+        <v>59</v>
+      </c>
+      <c r="C20" t="s">
+        <v>84</v>
+      </c>
+      <c r="D20" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" t="s">
+        <v>59</v>
+      </c>
+      <c r="C21" t="s">
+        <v>46</v>
+      </c>
+      <c r="D21" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C22" t="s">
+        <v>47</v>
+      </c>
+      <c r="D22" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23" t="s">
+        <v>59</v>
+      </c>
+      <c r="C23" t="s">
+        <v>48</v>
+      </c>
+      <c r="D23" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>28</v>
+      </c>
+      <c r="B24" t="s">
+        <v>59</v>
+      </c>
+      <c r="C24" t="s">
+        <v>49</v>
+      </c>
+      <c r="D24" t="s">
         <v>17</v>
       </c>
     </row>

--- a/database/excels/organization/base-seeder.xlsx
+++ b/database/excels/organization/base-seeder.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/monoland/Platform/monoland/database/excels/organization/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B79BF79C-9FC1-9C4B-BFF6-A425A59C9FDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{406F0947-9BC9-294B-9128-3304260F2C65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="500" windowWidth="33580" windowHeight="20500" activeTab="2" xr2:uid="{94E1010F-4E68-D749-BBCF-3803F804C4FE}"/>
+    <workbookView xWindow="20" yWindow="500" windowWidth="33580" windowHeight="20500" activeTab="1" xr2:uid="{94E1010F-4E68-D749-BBCF-3803F804C4FE}"/>
   </bookViews>
   <sheets>
     <sheet name="module" sheetId="2" r:id="rId1"/>
@@ -218,9 +218,6 @@
     <t>Jenis Jabatan</t>
   </si>
   <si>
-    <t>Jenis Peta Jabatan</t>
-  </si>
-  <si>
     <t>Peta Fungsional</t>
   </si>
   <si>
@@ -387,6 +384,9 @@
   </si>
   <si>
     <t>workunitread/:workunitread/formation</t>
+  </si>
+  <si>
+    <t>Tingkat Jabatan</t>
   </si>
 </sst>
 </file>
@@ -906,16 +906,16 @@
         <v>60</v>
       </c>
       <c r="D3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F3" t="s">
         <v>28</v>
       </c>
       <c r="G3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H3" s="4" t="b">
         <v>0</v>
@@ -929,22 +929,22 @@
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>118</v>
       </c>
       <c r="C4" t="s">
-        <v>62</v>
+        <v>118</v>
       </c>
       <c r="D4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F4" t="s">
         <v>28</v>
       </c>
       <c r="G4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H4" s="4" t="b">
         <v>0</v>
@@ -953,7 +953,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -967,16 +967,16 @@
         <v>61</v>
       </c>
       <c r="D5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F5" t="s">
         <v>28</v>
       </c>
       <c r="G5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H5" s="4" t="b">
         <v>0</v>
@@ -990,22 +990,22 @@
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F6" t="s">
         <v>28</v>
       </c>
       <c r="G6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H6" s="4" t="b">
         <v>0</v>
@@ -1019,22 +1019,22 @@
         <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F7" t="s">
         <v>28</v>
       </c>
       <c r="G7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H7" s="4" t="b">
         <v>0</v>
@@ -1043,7 +1043,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
@@ -1051,22 +1051,22 @@
         <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F8" t="s">
         <v>28</v>
       </c>
       <c r="G8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H8" s="4" t="b">
         <v>0</v>
@@ -1080,22 +1080,22 @@
         <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F9" t="s">
         <v>28</v>
       </c>
       <c r="G9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H9" s="4" t="b">
         <v>0</v>
@@ -1104,7 +1104,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
@@ -1121,13 +1121,13 @@
         <v>43</v>
       </c>
       <c r="E10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F10" t="s">
         <v>28</v>
       </c>
       <c r="G10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H10" s="4" t="b">
         <v>0</v>
@@ -1136,7 +1136,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
@@ -1150,16 +1150,16 @@
         <v>39</v>
       </c>
       <c r="D11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F11" t="s">
         <v>28</v>
       </c>
       <c r="G11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H11" s="4" t="b">
         <v>0</v>
@@ -1182,7 +1182,7 @@
         <v>42</v>
       </c>
       <c r="E12" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F12" t="s">
         <v>28</v>
@@ -1202,22 +1202,22 @@
         <v>28</v>
       </c>
       <c r="B13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F13" t="s">
         <v>28</v>
       </c>
       <c r="G13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H13" s="4" t="b">
         <v>0</v>
@@ -1231,22 +1231,22 @@
         <v>28</v>
       </c>
       <c r="B14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D14" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F14" t="s">
         <v>28</v>
       </c>
       <c r="G14" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H14" s="4" t="b">
         <v>0</v>
@@ -1255,7 +1255,7 @@
         <v>0</v>
       </c>
       <c r="J14" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
@@ -1292,22 +1292,22 @@
         <v>28</v>
       </c>
       <c r="B16" t="s">
+        <v>80</v>
+      </c>
+      <c r="C16" t="s">
+        <v>80</v>
+      </c>
+      <c r="D16" t="s">
         <v>81</v>
       </c>
-      <c r="C16" t="s">
-        <v>81</v>
-      </c>
-      <c r="D16" t="s">
-        <v>82</v>
-      </c>
       <c r="E16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F16" t="s">
         <v>28</v>
       </c>
       <c r="G16" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H16" s="4" t="b">
         <v>0</v>
@@ -1321,22 +1321,22 @@
         <v>28</v>
       </c>
       <c r="B17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D17" t="s">
         <v>45</v>
       </c>
       <c r="E17" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F17" t="s">
         <v>28</v>
       </c>
       <c r="G17" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H17" s="4" t="b">
         <v>0</v>
@@ -1345,7 +1345,7 @@
         <v>0</v>
       </c>
       <c r="J17" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
@@ -1353,22 +1353,22 @@
         <v>28</v>
       </c>
       <c r="B18" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D18" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E18" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F18" t="s">
         <v>28</v>
       </c>
       <c r="G18" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H18" s="4" t="b">
         <v>0</v>
@@ -1382,22 +1382,22 @@
         <v>28</v>
       </c>
       <c r="B19" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C19" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D19" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E19" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F19" t="s">
         <v>28</v>
       </c>
       <c r="G19" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H19" s="4" t="b">
         <v>0</v>
@@ -1406,7 +1406,7 @@
         <v>0</v>
       </c>
       <c r="J19" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
@@ -1414,22 +1414,22 @@
         <v>28</v>
       </c>
       <c r="B20" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C20" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D20" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E20" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F20" t="s">
         <v>28</v>
       </c>
       <c r="G20" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H20" s="4" t="b">
         <v>0</v>
@@ -1438,7 +1438,7 @@
         <v>0</v>
       </c>
       <c r="J20" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
@@ -1599,7 +1599,7 @@
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C3" t="s">
         <v>21</v>
@@ -1610,7 +1610,7 @@
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C4" t="s">
         <v>21</v>
@@ -1621,7 +1621,7 @@
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C5" t="s">
         <v>21</v>
@@ -1632,7 +1632,7 @@
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C6" t="s">
         <v>21</v>
@@ -1643,7 +1643,7 @@
         <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C7" t="s">
         <v>21</v>
@@ -1654,7 +1654,7 @@
         <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C8" t="s">
         <v>21</v>
@@ -1665,7 +1665,7 @@
         <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C9" t="s">
         <v>21</v>
@@ -1687,10 +1687,10 @@
         <v>28</v>
       </c>
       <c r="B11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -1709,7 +1709,7 @@
         <v>28</v>
       </c>
       <c r="B13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C13" t="s">
         <v>21</v>
@@ -1720,7 +1720,7 @@
         <v>28</v>
       </c>
       <c r="B14" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C14" t="s">
         <v>21</v>
@@ -1742,7 +1742,7 @@
         <v>28</v>
       </c>
       <c r="B16" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C16" t="s">
         <v>21</v>
@@ -1764,10 +1764,10 @@
         <v>28</v>
       </c>
       <c r="B18" t="s">
+        <v>97</v>
+      </c>
+      <c r="C18" t="s">
         <v>98</v>
-      </c>
-      <c r="C18" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -1775,7 +1775,7 @@
         <v>28</v>
       </c>
       <c r="B19" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C19" t="s">
         <v>21</v>
@@ -1786,7 +1786,7 @@
         <v>28</v>
       </c>
       <c r="B20" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C20" t="s">
         <v>21</v>
@@ -1800,7 +1800,7 @@
         <v>46</v>
       </c>
       <c r="C21" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -1811,7 +1811,7 @@
         <v>47</v>
       </c>
       <c r="C22" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -1822,7 +1822,7 @@
         <v>48</v>
       </c>
       <c r="C23" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -1919,7 +1919,7 @@
         <v>59</v>
       </c>
       <c r="C3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -1930,7 +1930,7 @@
         <v>59</v>
       </c>
       <c r="C4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -1941,7 +1941,7 @@
         <v>59</v>
       </c>
       <c r="C5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -1952,7 +1952,7 @@
         <v>59</v>
       </c>
       <c r="C6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -1963,7 +1963,7 @@
         <v>59</v>
       </c>
       <c r="C7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -1974,7 +1974,7 @@
         <v>59</v>
       </c>
       <c r="C8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -1985,7 +1985,7 @@
         <v>59</v>
       </c>
       <c r="C9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -2007,7 +2007,7 @@
         <v>59</v>
       </c>
       <c r="C11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -2029,7 +2029,7 @@
         <v>59</v>
       </c>
       <c r="C13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -2040,7 +2040,7 @@
         <v>59</v>
       </c>
       <c r="C14" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -2062,7 +2062,7 @@
         <v>59</v>
       </c>
       <c r="C16" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -2084,7 +2084,7 @@
         <v>59</v>
       </c>
       <c r="C18" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -2095,7 +2095,7 @@
         <v>59</v>
       </c>
       <c r="C19" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -2106,7 +2106,7 @@
         <v>59</v>
       </c>
       <c r="C20" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -2204,7 +2204,7 @@
         <v>59</v>
       </c>
       <c r="C3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D3" t="s">
         <v>17</v>
@@ -2218,7 +2218,7 @@
         <v>59</v>
       </c>
       <c r="C4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D4" t="s">
         <v>17</v>
@@ -2232,7 +2232,7 @@
         <v>59</v>
       </c>
       <c r="C5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D5" t="s">
         <v>17</v>
@@ -2246,7 +2246,7 @@
         <v>59</v>
       </c>
       <c r="C6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D6" t="s">
         <v>17</v>
@@ -2260,7 +2260,7 @@
         <v>59</v>
       </c>
       <c r="C7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D7" t="s">
         <v>17</v>
@@ -2274,7 +2274,7 @@
         <v>59</v>
       </c>
       <c r="C8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D8" t="s">
         <v>17</v>
@@ -2288,7 +2288,7 @@
         <v>59</v>
       </c>
       <c r="C9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D9" t="s">
         <v>17</v>
@@ -2316,7 +2316,7 @@
         <v>59</v>
       </c>
       <c r="C11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D11" t="s">
         <v>17</v>
@@ -2344,7 +2344,7 @@
         <v>59</v>
       </c>
       <c r="C13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D13" t="s">
         <v>17</v>
@@ -2358,7 +2358,7 @@
         <v>59</v>
       </c>
       <c r="C14" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D14" t="s">
         <v>17</v>
@@ -2386,7 +2386,7 @@
         <v>59</v>
       </c>
       <c r="C16" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D16" t="s">
         <v>17</v>
@@ -2414,7 +2414,7 @@
         <v>59</v>
       </c>
       <c r="C18" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D18" t="s">
         <v>17</v>
@@ -2428,7 +2428,7 @@
         <v>59</v>
       </c>
       <c r="C19" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D19" t="s">
         <v>17</v>
@@ -2442,7 +2442,7 @@
         <v>59</v>
       </c>
       <c r="C20" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D20" t="s">
         <v>17</v>
